--- a/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>BBNX</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,144 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>20400</v>
+      </c>
+      <c r="F8" s="3">
         <v>16700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
+        <v>12900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I8" s="3">
         <v>3100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F9" s="3">
         <v>7800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F10" s="3">
         <v>8900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -805,37 +832,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F12" s="3">
         <v>5100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I12" s="3">
         <v>3900</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -863,8 +898,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -892,8 +933,14 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -901,19 +948,19 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -921,8 +968,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -931,66 +984,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F17" s="3">
         <v>27700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
+        <v>22400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I17" s="3">
         <v>11900</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-8800</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1002,83 +1069,97 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-10300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-8800</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1089,37 +1170,49 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1147,8 +1240,14 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1176,66 +1275,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I26" s="3">
         <v>-8700</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I27" s="3">
         <v>-8700</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1263,8 +1380,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1292,8 +1415,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1321,8 +1450,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1350,66 +1485,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-8700</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1437,71 +1590,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-8700</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1513,8 +1684,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1526,25 +1699,27 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F41" s="3">
         <v>17500</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+      <c r="H41" s="3">
+        <v>26600</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1555,25 +1730,31 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>73100</v>
+      </c>
+      <c r="F42" s="3">
         <v>43400</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>70200</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1584,25 +1765,31 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F43" s="3">
         <v>7500</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>4400</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1613,25 +1800,31 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F44" s="3">
         <v>11300</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>1200</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1642,25 +1835,31 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>300</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1671,25 +1870,31 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>261900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>132900</v>
+      </c>
+      <c r="F46" s="3">
         <v>82600</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="H46" s="3">
+        <v>103600</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1700,13 +1905,19 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>64000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -1729,25 +1940,31 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F48" s="3">
         <v>11000</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="H48" s="3">
+        <v>6200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1758,8 +1975,14 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1769,17 +1992,17 @@
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -1787,8 +2010,14 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1816,8 +2045,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1845,25 +2080,31 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>300</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>200</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -1874,8 +2115,14 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1903,25 +2150,31 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>149600</v>
+      </c>
+      <c r="F54" s="3">
         <v>96900</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="H54" s="3">
+        <v>110000</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1932,8 +2185,14 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1945,8 +2204,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1958,25 +2219,27 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3">
+        <v>1200</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2250,14 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -1996,19 +2265,19 @@
         <v>1500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2016,25 +2285,31 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3">
+        <v>1100</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2045,25 +2320,31 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F60" s="3">
         <v>17900</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="H60" s="3">
+        <v>10600</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2074,25 +2355,31 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F61" s="3">
         <v>5900</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2103,25 +2390,31 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
+        <v>44900</v>
+      </c>
+      <c r="F62" s="3">
         <v>38900</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>37600</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2132,8 +2425,14 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2161,8 +2460,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2190,8 +2495,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2219,25 +2530,31 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>73600</v>
+      </c>
+      <c r="F66" s="3">
         <v>64100</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="H66" s="3">
+        <v>51400</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2248,8 +2565,14 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2261,8 +2584,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2290,8 +2615,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2319,25 +2650,31 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>321400</v>
+      </c>
+      <c r="F70" s="3">
         <v>261700</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>261700</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>261700</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -2348,8 +2685,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2377,25 +2720,31 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-325400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-296700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-278600</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>-229700</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2406,8 +2755,14 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2435,8 +2790,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2464,8 +2825,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2493,25 +2860,31 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>313800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-245400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-228800</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+      <c r="G76" s="3">
+        <v>-203100</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-203100</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2522,8 +2895,14 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2551,71 +2930,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-8700</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2627,13 +3024,15 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>500</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
@@ -2656,8 +3055,14 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2685,8 +3090,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2714,8 +3125,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2743,8 +3160,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2772,8 +3195,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2801,25 +3230,31 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-14300</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="G89" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-6300</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2830,8 +3265,14 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2843,25 +3284,27 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-600</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="G91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-300</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -2872,8 +3315,14 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2901,8 +3350,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2930,25 +3385,31 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-179100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-29700</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>7600</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-69600</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -2959,8 +3420,14 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2972,8 +3439,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3001,8 +3470,14 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3030,8 +3505,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3059,8 +3540,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3088,25 +3575,31 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>211100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>56900</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3117,8 +3610,14 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3146,33 +3645,45 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-75900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>BBNX</t>
   </si>
@@ -656,55 +656,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,32 +715,35 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E8" s="3">
         <v>17600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -749,32 +753,35 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E9" s="3">
         <v>8700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,32 +791,35 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E10" s="3">
         <v>9000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1200</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,8 +829,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -834,32 +847,33 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3900</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -869,8 +883,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -904,8 +921,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -939,8 +959,11 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -948,10 +971,10 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -963,7 +986,7 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -974,8 +997,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -986,32 +1012,33 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E17" s="3">
         <v>36300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11900</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,32 +1048,35 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8800</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1056,8 +1086,11 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1071,32 +1104,33 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>12500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1106,32 +1140,35 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8800</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
@@ -1141,28 +1178,31 @@
       <c r="M21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1176,32 +1216,35 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8700</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1211,8 +1254,11 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1246,8 +1292,11 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1281,32 +1330,35 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8700</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,32 +1368,35 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8700</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1406,11 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1386,8 +1444,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1421,8 +1482,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1456,8 +1520,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1491,32 +1558,35 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1526,32 +1596,35 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8700</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1561,8 +1634,11 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1596,32 +1672,35 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8700</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1631,37 +1710,40 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1671,8 +1753,11 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1686,8 +1771,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1701,29 +1787,30 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E41" s="3">
         <v>42500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17500</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>26600</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1736,29 +1823,32 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>214600</v>
+      </c>
+      <c r="E42" s="3">
         <v>189000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>43400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>70200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1771,29 +1861,32 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E43" s="3">
         <v>9100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>4400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,29 +1899,32 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E44" s="3">
         <v>15700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11300</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,29 +1937,32 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,29 +1975,32 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E46" s="3">
         <v>261900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>132900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>82600</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
         <v>103600</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1911,17 +2013,20 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E47" s="3">
         <v>64000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1946,29 +2051,32 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E48" s="3">
         <v>11900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>6200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,8 +2089,11 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2004,8 +2115,8 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2016,8 +2127,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2051,8 +2165,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,8 +2203,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2095,20 +2215,20 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,8 +2241,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2156,29 +2279,32 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E54" s="3">
         <v>338000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>149600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96900</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3">
         <v>110000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,8 +2317,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2206,8 +2335,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2221,29 +2351,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2256,8 +2387,11 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2271,16 +2405,16 @@
         <v>1500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2291,29 +2425,32 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,29 +2463,32 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E60" s="3">
         <v>16500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17900</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>10600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,29 +2501,32 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E61" s="3">
         <v>5500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5900</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>3000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2396,29 +2539,32 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>44900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38900</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>37600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2431,8 +2577,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2466,8 +2615,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,8 +2653,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2536,29 +2691,32 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E66" s="3">
         <v>24300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>64100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3">
         <v>51400</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2571,8 +2729,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2586,8 +2747,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2621,8 +2783,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2656,8 +2821,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2665,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>321400</v>
-      </c>
-      <c r="F70" s="3">
-        <v>261700</v>
       </c>
       <c r="G70" s="3">
         <v>261700</v>
@@ -2677,7 +2845,7 @@
         <v>261700</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>261700</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2691,8 +2859,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2726,29 +2897,32 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-342300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-325400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-296700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-278600</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-229700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2761,8 +2935,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2796,8 +2973,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2831,8 +3011,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2866,28 +3049,31 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E76" s="3">
         <v>313800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-245400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-228800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-203100</v>
       </c>
       <c r="H76" s="3">
         <v>-203100</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>-203100</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2901,8 +3087,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2936,37 +3125,40 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2976,32 +3168,35 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8700</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3011,8 +3206,11 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3026,17 +3224,18 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3260,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3096,8 +3298,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3131,8 +3336,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3166,8 +3374,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3201,8 +3412,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3236,29 +3450,32 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14300</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-12100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3271,8 +3488,11 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3286,29 +3506,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3321,8 +3542,11 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3356,8 +3580,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3391,29 +3618,32 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-179100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29700</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>7600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-69600</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3426,8 +3656,11 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3441,8 +3674,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3476,8 +3710,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3511,8 +3748,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3546,8 +3786,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3581,28 +3824,31 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>211100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56900</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3616,8 +3862,11 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3651,39 +3900,45 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-4500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-75900</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>BBNX</t>
   </si>
@@ -656,64 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,38 +723,41 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E8" s="3">
         <v>27300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -764,38 +767,41 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E9" s="3">
         <v>12100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,38 +811,41 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E10" s="3">
         <v>15100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -846,8 +855,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,38 +875,39 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E12" s="3">
         <v>8200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3900</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,8 +917,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +961,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,25 +1005,28 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
       </c>
       <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1016,7 +1038,7 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1027,8 +1049,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,38 +1066,39 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E17" s="3">
         <v>44300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>26800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11900</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1082,38 +1108,41 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1123,8 +1152,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,8 +1172,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1152,26 +1185,26 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>12500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1181,38 +1214,41 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-30800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8800</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
@@ -1222,8 +1258,11 @@
       <c r="O21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1236,8 +1275,8 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1263,38 +1302,41 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,8 +1346,11 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1345,8 +1390,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,38 +1434,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8700</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,38 +1478,41 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,8 +1522,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1566,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,8 +1698,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1644,26 +1713,26 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-12500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,38 +1742,41 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1786,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,38 +1830,41 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1796,43 +1874,46 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1842,8 +1923,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,29 +1961,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E41" s="3">
         <v>38500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17500</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,29 +2003,32 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E42" s="3">
         <v>190200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>214600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>189000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>43400</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1958,29 +2047,32 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E43" s="3">
         <v>14300</v>
       </c>
-      <c r="E43" s="3">
-        <v>11400</v>
-      </c>
       <c r="F43" s="3">
+        <v>13400</v>
+      </c>
+      <c r="G43" s="3">
         <v>11000</v>
       </c>
-      <c r="G43" s="3">
-        <v>12000</v>
-      </c>
       <c r="H43" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I43" s="3">
         <v>7500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,29 +2091,32 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E44" s="3">
         <v>20400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,28 +2135,31 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2300</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
       </c>
       <c r="G45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
+        <v>300</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2081,29 +2179,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>267900</v>
+      </c>
+      <c r="E46" s="3">
         <v>270000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>286100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>261900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>132900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>82600</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,23 +2223,26 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E47" s="3">
         <v>45300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>64000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2163,29 +2267,32 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E48" s="3">
         <v>14400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,8 +2311,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2233,8 +2343,8 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2245,8 +2355,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,28 +2443,31 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>300</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2368,8 +2487,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,29 +2531,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>330000</v>
+        <v>328700</v>
       </c>
       <c r="E54" s="3">
         <v>330000</v>
       </c>
       <c r="F54" s="3">
+        <v>330000</v>
+      </c>
+      <c r="G54" s="3">
         <v>338000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>149600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>96900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,8 +2575,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,29 +2613,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,16 +2655,19 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1500</v>
       </c>
       <c r="F58" s="3">
         <v>1500</v>
@@ -2546,7 +2679,7 @@
         <v>1500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2554,8 +2687,8 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2566,29 +2699,32 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,29 +2743,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E60" s="3">
         <v>25400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17900</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,29 +2787,32 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2689,29 +2831,32 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>44900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38900</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2730,8 +2875,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,29 +3007,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E66" s="3">
         <v>35300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>73600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>64100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,8 +3051,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3008,20 +3175,20 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>321400</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>261700</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>261700</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3034,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,29 +3245,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-369900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-356500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-342300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-325400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-296700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-278600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,8 +3289,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,35 +3421,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>287600</v>
+      </c>
+      <c r="E76" s="3">
         <v>294800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>301600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>313800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-245400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-228800</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
         <v>-203100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3280,8 +3465,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,43 +3509,46 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3367,38 +3558,41 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3408,8 +3602,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,13 +3622,14 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -3440,11 +3638,11 @@
         <v>600</v>
       </c>
       <c r="G83" s="3">
+        <v>600</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3664,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,35 +3884,38 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12100</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3928,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,35 +3948,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,8 +3990,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,35 +4078,38 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>9500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-179100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3893,8 +4122,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4142,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3951,8 +4184,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,34 +4316,37 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>211100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>56900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
@@ -4115,8 +4360,11 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4156,45 +4404,51 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E102" s="3">
         <v>3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4500</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBNX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>BBNX</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,41 +727,44 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E8" s="3">
         <v>32100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -770,41 +774,44 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E9" s="3">
         <v>13200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -814,41 +821,44 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E10" s="3">
         <v>18900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,41 +889,42 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E12" s="3">
         <v>10100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3900</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,28 +1028,31 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1041,7 +1064,7 @@
         <v>300</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,41 +1093,42 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E17" s="3">
         <v>48200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1111,41 +1138,44 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,13 +1206,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1188,26 +1222,26 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>12500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1217,41 +1251,44 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-15600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8800</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
@@ -1261,8 +1298,11 @@
       <c r="P21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,41 +1345,44 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,8 +1392,11 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,41 +1486,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8700</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,41 +1533,44 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,13 +1768,16 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1716,26 +1786,26 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-12500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1745,41 +1815,44 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1789,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,41 +1909,44 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,46 +1956,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2008,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,32 +2048,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E41" s="3">
         <v>31600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,32 +2093,35 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>169300</v>
+      </c>
+      <c r="E42" s="3">
         <v>187500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>190200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>214600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>189000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>73100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>43400</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2050,32 +2140,35 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E43" s="3">
         <v>19900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,32 +2187,35 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E44" s="3">
         <v>21700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11300</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,16 +2234,19 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
-        <v>300</v>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
@@ -2155,14 +2254,14 @@
       <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
+        <v>300</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2182,32 +2281,35 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E46" s="3">
         <v>267900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>270000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>286100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>261900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>132900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>82600</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,26 +2328,29 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E47" s="3">
         <v>45400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>64000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2270,32 +2375,35 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E48" s="3">
         <v>15200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2314,8 +2422,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2346,8 +2457,8 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2563,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2455,22 +2575,22 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>300</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,32 +2657,35 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>304400</v>
+      </c>
+      <c r="E54" s="3">
         <v>328700</v>
-      </c>
-      <c r="E54" s="3">
-        <v>330000</v>
       </c>
       <c r="F54" s="3">
         <v>330000</v>
       </c>
       <c r="G54" s="3">
+        <v>330000</v>
+      </c>
+      <c r="H54" s="3">
         <v>338000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>149600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>96900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,32 +2744,33 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,19 +2789,22 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1500</v>
       </c>
       <c r="G58" s="3">
         <v>1500</v>
@@ -2682,7 +2816,7 @@
         <v>1500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2690,8 +2824,8 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2702,32 +2836,35 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,32 +2883,35 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E60" s="3">
         <v>30900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17900</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,32 +2930,35 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E61" s="3">
         <v>5400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2834,32 +2977,35 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>44900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38900</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,32 +3165,35 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E66" s="3">
         <v>41100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>73600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>64100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3178,20 +3346,20 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>321400</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>261700</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>261700</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,32 +3419,35 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-391800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-369900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-356500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-342300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-325400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-296700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-278600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,38 +3607,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271200</v>
+      </c>
+      <c r="E76" s="3">
         <v>287600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>294800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>301600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>313800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-245400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-228800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>-203100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,46 +3701,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,41 +3753,44 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,16 +3821,17 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -3641,11 +3840,11 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3667,8 +3866,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,38 +4101,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,8 +4148,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,38 +4169,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,38 +4308,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-179100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4355,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,37 +4562,40 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>211100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4363,8 +4609,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,48 +4656,54 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4500</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
